--- a/docs/downloads/04/tbl_raison_alaotra_mangabe.xlsx
+++ b/docs/downloads/04/tbl_raison_alaotra_mangabe.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -466,12 +466,6 @@
           <t>Travail non agricole</t>
         </is>
       </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>4.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -535,12 +529,6 @@
           <t>Travail agricole</t>
         </is>
       </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>3.9</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -558,12 +546,6 @@
           <t>Travail non agricole</t>
         </is>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -578,14 +560,8 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Accès terre</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>0.2</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -601,14 +577,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Autre</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="E11">
-        <v>0.2</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="12">
@@ -624,14 +600,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D12">
-        <v>51</v>
+        <v>371</v>
       </c>
       <c r="E12">
-        <v>10.1</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="13">
@@ -647,14 +623,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D13">
-        <v>371</v>
+        <v>46</v>
       </c>
       <c r="E13">
-        <v>73.3</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="14">
@@ -670,14 +646,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Suivi famille</t>
+          <t>Travail non agricole</t>
         </is>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="E14">
-        <v>0.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="15">
@@ -688,19 +664,13 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>46</v>
-      </c>
-      <c r="E15">
-        <v>9.1</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -711,19 +681,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D16">
-        <v>35</v>
+        <v>113</v>
       </c>
       <c r="E16">
-        <v>6.9</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="17">
@@ -739,14 +709,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Accès terre</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>216</v>
       </c>
       <c r="E17">
-        <v>0.3</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="18">
@@ -762,14 +732,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D18">
-        <v>113</v>
+        <v>25</v>
       </c>
       <c r="E18">
-        <v>30.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="19">
@@ -785,82 +755,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Travail non agricole</t>
         </is>
       </c>
       <c r="D19">
-        <v>216</v>
+        <v>15</v>
       </c>
       <c r="E19">
-        <v>58.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Suivi famille</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>25</v>
-      </c>
-      <c r="E21">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>15</v>
-      </c>
-      <c r="E22">
         <v>4</v>
       </c>
     </row>

--- a/docs/downloads/04/tbl_raison_alaotra_mangabe.xlsx
+++ b/docs/downloads/04/tbl_raison_alaotra_mangabe.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,14 +394,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="E2">
-        <v>13.7</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="3">
@@ -417,14 +417,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Économique (travail, ressources)</t>
         </is>
       </c>
       <c r="D3">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>74</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -435,19 +435,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="E4">
-        <v>8.199999999999999</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -458,93 +458,93 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
+          <t>Économique (travail, ressources)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>33.3</v>
+          <t>Autre / NSP</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>31</v>
-      </c>
-      <c r="E7">
-        <v>60.8</v>
+          <t>Conjoncturelle (écologie, insécurité)</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
+          <t>Sociale (naissance, mariage, famille)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>457</v>
+      </c>
+      <c r="E8">
+        <v>90.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
+          <t>Économique (travail, ressources)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>47</v>
+      </c>
+      <c r="E9">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -555,12 +555,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Autre raison</t>
+          <t>Conjoncturelle (écologie, insécurité)</t>
         </is>
       </c>
     </row>
@@ -572,19 +572,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D11">
-        <v>51</v>
+        <v>344</v>
       </c>
       <c r="E11">
-        <v>10.1</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="12">
@@ -595,174 +595,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Économique (travail, ressources)</t>
         </is>
       </c>
       <c r="D12">
-        <v>371</v>
+        <v>26</v>
       </c>
       <c r="E12">
-        <v>73.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>46</v>
-      </c>
-      <c r="E13">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>35</v>
-      </c>
-      <c r="E14">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Autre raison</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>113</v>
-      </c>
-      <c r="E16">
-        <v>30.5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>216</v>
-      </c>
-      <c r="E17">
-        <v>58.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>25</v>
-      </c>
-      <c r="E18">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>15</v>
-      </c>
-      <c r="E19">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
